--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.2361,0.5651,0.0116,0.2662</t>
-  </si>
-  <si>
-    <t>0.1085,0.0118,0.0005,0.9524</t>
-  </si>
-  <si>
-    <t>0.7437,0.0136,0.0038,0.2851</t>
-  </si>
-  <si>
-    <t>0.0989,0.0038,0.0053,0.9585</t>
-  </si>
-  <si>
-    <t>0.9961,0.0012,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9951,0.0015,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9720,0.0280,0.0050,0.0013</t>
-  </si>
-  <si>
-    <t>0.9904,0.0074,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9793,0.0273,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9600,0.0436,0.0052,0.0019</t>
-  </si>
-  <si>
-    <t>0.9878,0.0097,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9940,0.0019,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.6674,0.0149,0.3980,0.0109</t>
-  </si>
-  <si>
-    <t>0.1703,0.0157,0.8586,0.0112</t>
-  </si>
-  <si>
-    <t>0.5799,0.0150,0.5764,0.0007</t>
-  </si>
-  <si>
-    <t>0.0507,0.0094,0.9561,0.0007</t>
-  </si>
-  <si>
-    <t>0.7313,0.0431,0.2592,0.0265</t>
-  </si>
-  <si>
-    <t>0.0026,0.9907,0.0191,0.0013</t>
-  </si>
-  <si>
-    <t>0.0006,0.9968,0.0165,0.0001</t>
-  </si>
-  <si>
-    <t>0.1504,0.8740,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.0150,0.9784,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.0049,0.9908,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.6370,0.0096,0.4580,0.0078</t>
-  </si>
-  <si>
-    <t>0.3946,0.0523,0.5957,0.0056</t>
-  </si>
-  <si>
-    <t>0.0126,0.0172,0.9711,0.0016</t>
-  </si>
-  <si>
-    <t>0.1182,0.0543,0.8528,0.0087</t>
-  </si>
-  <si>
-    <t>0.5683,0.0029,0.6652,0.0011</t>
-  </si>
-  <si>
-    <t>0.0291,0.0029,0.9633,0.0063</t>
-  </si>
-  <si>
-    <t>0.0083,0.0012,0.9867,0.0042</t>
-  </si>
-  <si>
-    <t>0.4617,0.5648,0.0335,0.0087</t>
-  </si>
-  <si>
-    <t>0.7403,0.2427,0.0645,0.0059</t>
-  </si>
-  <si>
-    <t>0.0005,0.0053,0.9965,0.0032</t>
-  </si>
-  <si>
-    <t>0.0070,0.9767,0.0337,0.0004</t>
-  </si>
-  <si>
-    <t>0.9240,0.0447,0.0181,0.0120</t>
-  </si>
-  <si>
-    <t>0.8545,0.0900,0.0631,0.0149</t>
-  </si>
-  <si>
-    <t>0.9054,0.1186,0.0048,0.0011</t>
-  </si>
-  <si>
-    <t>0.0355,0.9513,0.0799,0.0045</t>
-  </si>
-  <si>
-    <t>0.0129,0.7582,0.4570,0.0428</t>
-  </si>
-  <si>
-    <t>0.1087,0.0495,0.8548,0.0208</t>
-  </si>
-  <si>
-    <t>0.0747,0.0364,0.9107,0.0081</t>
-  </si>
-  <si>
-    <t>0.0911,0.0215,0.6943,0.2067</t>
-  </si>
-  <si>
-    <t>0.0151,0.6808,0.8390,0.0016</t>
-  </si>
-  <si>
-    <t>0.0089,0.9661,0.0300,0.0051</t>
-  </si>
-  <si>
-    <t>0.0114,0.1957,0.9420,0.0052</t>
-  </si>
-  <si>
-    <t>0.1071,0.6339,0.0255,0.6653</t>
-  </si>
-  <si>
-    <t>0.0135,0.9795,0.0035,0.0016</t>
-  </si>
-  <si>
-    <t>0.0021,0.9873,0.0399,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9978,0.0134,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.1116,0.9792,0.0016</t>
-  </si>
-  <si>
-    <t>0.0072,0.0146,0.9880,0.0006</t>
-  </si>
-  <si>
-    <t>0.0194,0.0038,0.9655,0.0154</t>
-  </si>
-  <si>
-    <t>0.0264,0.0010,0.9775,0.0023</t>
-  </si>
-  <si>
-    <t>0.0028,0.0226,0.9836,0.0087</t>
-  </si>
-  <si>
-    <t>0.0014,0.0480,0.9836,0.0024</t>
-  </si>
-  <si>
-    <t>0.8760,0.1760,0.0079,0.0049</t>
-  </si>
-  <si>
-    <t>0.9219,0.0622,0.0146,0.0074</t>
-  </si>
-  <si>
-    <t>0.9829,0.0113,0.0015,0.0019</t>
-  </si>
-  <si>
-    <t>0.0038,0.0425,0.9893,0.0029</t>
-  </si>
-  <si>
-    <t>0.9914,0.0034,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9802,0.0107,0.0047,0.0022</t>
-  </si>
-  <si>
-    <t>0.9723,0.0182,0.0070,0.0020</t>
-  </si>
-  <si>
-    <t>0.0012,0.8024,0.9755,0.0006</t>
-  </si>
-  <si>
-    <t>0.0034,0.0109,0.9924,0.0008</t>
-  </si>
-  <si>
-    <t>0.0039,0.0210,0.9899,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.9586,0.9598,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.0053,0.9933,0.0007</t>
-  </si>
-  <si>
-    <t>0.0853,0.7676,0.1651,0.0015</t>
-  </si>
-  <si>
-    <t>0.0066,0.9899,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9571,0.0223,0.0199,0.0012</t>
-  </si>
-  <si>
-    <t>0.5951,0.2429,0.2500,0.0181</t>
-  </si>
-  <si>
-    <t>0.0072,0.0589,0.9599,0.0170</t>
-  </si>
-  <si>
-    <t>0.0015,0.9381,0.5575,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9850,0.9098,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9952,0.7158,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9957,0.0875,0.0000</t>
-  </si>
-  <si>
-    <t>0.0152,0.0022,0.0057,0.9880</t>
-  </si>
-  <si>
-    <t>0.0017,0.0025,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0011,0.1000,0.0010,0.9968</t>
-  </si>
-  <si>
-    <t>0.0183,0.0150,0.0057,0.9863</t>
-  </si>
-  <si>
-    <t>0.0108,0.0034,0.0028,0.9932</t>
-  </si>
-  <si>
-    <t>0.0030,0.0001,0.0068,0.9950</t>
-  </si>
-  <si>
-    <t>0.0004,0.9885,0.8678,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.8351,0.9319,0.0006</t>
-  </si>
-  <si>
-    <t>0.0051,0.9298,0.4999,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.8954,0.9808,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9750,0.5196,0.0005</t>
-  </si>
-  <si>
-    <t>0.0167,0.7457,0.7976,0.0045</t>
-  </si>
-  <si>
-    <t>0.9959,0.0041,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9893,0.0069,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9719,0.0357,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.9769,0.0092,0.0021,0.0042</t>
-  </si>
-  <si>
-    <t>0.9759,0.0181,0.0023,0.0015</t>
-  </si>
-  <si>
-    <t>0.9967,0.0014,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9821,0.0147,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.9561,0.0429,0.0083,0.0016</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9941,0.0016,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9964,0.0008,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9953,0.0012,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9968,0.0008,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0005,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9962,0.0012,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0034,0.0012,0.9927,0.0039</t>
-  </si>
-  <si>
-    <t>0.1605,0.1079,0.7345,0.0027</t>
-  </si>
-  <si>
-    <t>0.5599,0.0138,0.3140,0.0853</t>
-  </si>
-  <si>
-    <t>0.0524,0.0022,0.9616,0.0011</t>
-  </si>
-  <si>
-    <t>0.0162,0.9823,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.9949,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.0178,0.9724,0.0022,0.0028</t>
-  </si>
-  <si>
-    <t>0.3610,0.6967,0.0220,0.0023</t>
-  </si>
-  <si>
-    <t>0.0162,0.9717,0.0052,0.0017</t>
-  </si>
-  <si>
-    <t>0.0007,0.9970,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.6281,0.4875,0.0085,0.0016</t>
-  </si>
-  <si>
-    <t>0.8556,0.0394,0.1155,0.0033</t>
-  </si>
-  <si>
-    <t>0.3724,0.0044,0.8005,0.0013</t>
-  </si>
-  <si>
-    <t>0.7410,0.0680,0.1226,0.0229</t>
-  </si>
-  <si>
-    <t>0.5264,0.0844,0.4431,0.0247</t>
-  </si>
-  <si>
-    <t>0.2939,0.0470,0.5644,0.2480</t>
-  </si>
-  <si>
-    <t>0.0055,0.9872,0.0045,0.0015</t>
-  </si>
-  <si>
-    <t>0.0059,0.9809,0.0170,0.0044</t>
-  </si>
-  <si>
-    <t>0.1058,0.8266,0.0295,0.0931</t>
-  </si>
-  <si>
-    <t>0.0013,0.9556,0.7554,0.0019</t>
-  </si>
-  <si>
-    <t>0.0214,0.9777,0.0250,0.0002</t>
-  </si>
-  <si>
-    <t>0.5908,0.5046,0.0180,0.0029</t>
-  </si>
-  <si>
-    <t>0.6319,0.4502,0.0141,0.0070</t>
-  </si>
-  <si>
-    <t>0.9682,0.0433,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9896,0.0078,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9880,0.0047,0.0014,0.0025</t>
-  </si>
-  <si>
-    <t>0.9866,0.0036,0.0011,0.0029</t>
-  </si>
-  <si>
-    <t>0.9858,0.0023,0.0005,0.0059</t>
-  </si>
-  <si>
-    <t>0.9812,0.0050,0.0085,0.0018</t>
-  </si>
-  <si>
-    <t>0.9841,0.0038,0.0028,0.0046</t>
-  </si>
-  <si>
-    <t>0.9889,0.0051,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.0047,0.4156,0.9567,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.9049,0.8115,0.0001</t>
-  </si>
-  <si>
-    <t>0.0143,0.7490,0.8203,0.0023</t>
-  </si>
-  <si>
-    <t>0.0141,0.0577,0.9591,0.0004</t>
-  </si>
-  <si>
-    <t>0.7135,0.0166,0.2571,0.0353</t>
-  </si>
-  <si>
-    <t>0.9159,0.0138,0.0767,0.0028</t>
-  </si>
-  <si>
-    <t>0.7758,0.0035,0.3316,0.0057</t>
-  </si>
-  <si>
-    <t>0.7924,0.0332,0.1755,0.0114</t>
-  </si>
-  <si>
-    <t>0.1105,0.0018,0.0050,0.9523</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0008,0.9992</t>
-  </si>
-  <si>
-    <t>0.0071,0.0005,0.0001,0.9975</t>
-  </si>
-  <si>
-    <t>0.0063,0.0177,0.0033,0.9939</t>
-  </si>
-  <si>
-    <t>0.0054,0.9291,0.5608,0.0040</t>
-  </si>
-  <si>
-    <t>0.9771,0.0158,0.0038,0.0012</t>
-  </si>
-  <si>
-    <t>0.0966,0.8901,0.0058,0.0258</t>
-  </si>
-  <si>
-    <t>0.9780,0.0062,0.0038,0.0045</t>
-  </si>
-  <si>
-    <t>0.8566,0.1649,0.0128,0.0031</t>
-  </si>
-  <si>
-    <t>0.9692,0.0065,0.0048,0.0105</t>
-  </si>
-  <si>
-    <t>0.6151,0.0078,0.0214,0.4287</t>
-  </si>
-  <si>
-    <t>0.9655,0.0273,0.0053,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.0299,0.9975,0.0020</t>
-  </si>
-  <si>
-    <t>0.8566,0.0004,0.0004,0.3062</t>
-  </si>
-  <si>
-    <t>0.9454,0.0083,0.0063,0.0252</t>
-  </si>
-  <si>
-    <t>0.8328,0.2021,0.0111,0.0060</t>
-  </si>
-  <si>
-    <t>0.8780,0.0586,0.0356,0.0088</t>
-  </si>
-  <si>
-    <t>0.9434,0.0300,0.0246,0.0013</t>
-  </si>
-  <si>
-    <t>0.5825,0.2106,0.2840,0.0319</t>
-  </si>
-  <si>
-    <t>0.7755,0.1941,0.0569,0.0044</t>
-  </si>
-  <si>
-    <t>0.9114,0.0583,0.0217,0.0048</t>
-  </si>
-  <si>
-    <t>0.9835,0.0060,0.0017,0.0025</t>
-  </si>
-  <si>
-    <t>0.9637,0.0159,0.0036,0.0092</t>
-  </si>
-  <si>
-    <t>0.9947,0.0021,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9923,0.0022,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.9692,0.0373,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.9881,0.0042,0.0011,0.0016</t>
-  </si>
-  <si>
-    <t>0.9870,0.0018,0.0006,0.0047</t>
-  </si>
-  <si>
-    <t>0.9918,0.0024,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9335,0.0735,0.0039,0.0024</t>
-  </si>
-  <si>
-    <t>0.6235,0.4684,0.0270,0.0011</t>
-  </si>
-  <si>
-    <t>0.2320,0.8088,0.0070,0.0022</t>
-  </si>
-  <si>
-    <t>0.2466,0.5370,0.4473,0.0162</t>
-  </si>
-  <si>
-    <t>0.8203,0.2002,0.0298,0.0025</t>
-  </si>
-  <si>
-    <t>0.9215,0.0613,0.0196,0.0090</t>
-  </si>
-  <si>
-    <t>0.9671,0.0395,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.2998,0.7688,0.0027,0.0032</t>
-  </si>
-  <si>
-    <t>0.0005,0.0095,0.9983,0.0005</t>
-  </si>
-  <si>
-    <t>0.9165,0.0857,0.0139,0.0031</t>
-  </si>
-  <si>
-    <t>0.0030,0.0044,0.9934,0.0003</t>
-  </si>
-  <si>
-    <t>0.0033,0.0192,0.9825,0.0052</t>
-  </si>
-  <si>
-    <t>0.0172,0.0016,0.9839,0.0011</t>
-  </si>
-  <si>
-    <t>0.0071,0.0680,0.9783,0.0010</t>
-  </si>
-  <si>
-    <t>0.1294,0.0082,0.8998,0.0033</t>
-  </si>
-  <si>
-    <t>0.0605,0.0113,0.9503,0.0006</t>
-  </si>
-  <si>
-    <t>0.0552,0.0028,0.9623,0.0005</t>
-  </si>
-  <si>
-    <t>0.4408,0.1188,0.4760,0.0101</t>
-  </si>
-  <si>
-    <t>0.4420,0.0088,0.7040,0.0030</t>
-  </si>
-  <si>
-    <t>0.2376,0.0531,0.7542,0.0114</t>
-  </si>
-  <si>
-    <t>0.5817,0.2977,0.1308,0.0060</t>
-  </si>
-  <si>
-    <t>0.0423,0.8618,0.0906,0.0019</t>
-  </si>
-  <si>
-    <t>0.4224,0.3090,0.1931,0.0077</t>
-  </si>
-  <si>
-    <t>0.7806,0.0638,0.1253,0.0264</t>
-  </si>
-  <si>
-    <t>0.3767,0.0813,0.6366,0.0061</t>
-  </si>
-  <si>
-    <t>0.8773,0.2193,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.9135,0.1843,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.6842,0.3997,0.0084,0.0045</t>
-  </si>
-  <si>
-    <t>0.9282,0.1142,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.5123,0.5893,0.0111,0.0014</t>
-  </si>
-  <si>
-    <t>0.7682,0.0263,0.2781,0.0041</t>
-  </si>
-  <si>
-    <t>0.8789,0.0083,0.1151,0.0074</t>
-  </si>
-  <si>
-    <t>0.8794,0.0134,0.0538,0.0223</t>
-  </si>
-  <si>
-    <t>0.6109,0.0486,0.4177,0.0082</t>
-  </si>
-  <si>
-    <t>0.8235,0.0549,0.1039,0.0291</t>
-  </si>
-  <si>
-    <t>0.0355,0.0344,0.8366,0.1730</t>
-  </si>
-  <si>
-    <t>0.0518,0.1601,0.8737,0.0088</t>
-  </si>
-  <si>
-    <t>0.0331,0.0991,0.9470,0.0010</t>
-  </si>
-  <si>
-    <t>0.0341,0.0402,0.9493,0.0029</t>
-  </si>
-  <si>
-    <t>0.0187,0.6725,0.6810,0.0048</t>
-  </si>
-  <si>
-    <t>0.9517,0.0216,0.0081,0.0106</t>
-  </si>
-  <si>
-    <t>0.9748,0.0193,0.0065,0.0009</t>
-  </si>
-  <si>
-    <t>0.9812,0.0178,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9926,0.0021,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9883,0.0079,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9843,0.0123,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9884,0.0105,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9900,0.0024,0.0009,0.0022</t>
-  </si>
-  <si>
-    <t>0.1637,0.0302,0.8469,0.0092</t>
-  </si>
-  <si>
-    <t>0.1606,0.3122,0.6943,0.0066</t>
-  </si>
-  <si>
-    <t>0.7867,0.0168,0.0749,0.0807</t>
-  </si>
-  <si>
-    <t>0.0167,0.0120,0.9808,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.0503,0.9808,0.0031</t>
-  </si>
-  <si>
-    <t>0.0036,0.0136,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0025,0.9978,0.0005</t>
-  </si>
-  <si>
-    <t>0.1591,0.0211,0.8541,0.0025</t>
-  </si>
-  <si>
-    <t>0.0010,0.0096,0.9952,0.0007</t>
-  </si>
-  <si>
-    <t>0.0075,0.0127,0.9791,0.0023</t>
-  </si>
-  <si>
-    <t>0.2659,0.0646,0.6995,0.0039</t>
-  </si>
-  <si>
-    <t>0.7797,0.0106,0.2410,0.0073</t>
-  </si>
-  <si>
-    <t>0.8119,0.0057,0.3282,0.0014</t>
-  </si>
-  <si>
-    <t>0.8550,0.0417,0.0586,0.0335</t>
-  </si>
-  <si>
-    <t>0.9815,0.0140,0.0029,0.0010</t>
-  </si>
-  <si>
-    <t>0.9690,0.0310,0.0063,0.0007</t>
-  </si>
-  <si>
-    <t>0.9926,0.0041,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9815,0.0166,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9962,0.0002,0.0000,0.0020</t>
-  </si>
-  <si>
-    <t>0.9623,0.0488,0.0033,0.0012</t>
-  </si>
-  <si>
-    <t>0.9921,0.0049,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9882,0.0090,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0223,0.1013,0.8978,0.0033</t>
-  </si>
-  <si>
-    <t>0.0005,0.1040,0.9861,0.0032</t>
-  </si>
-  <si>
-    <t>0.0021,0.0924,0.9791,0.0018</t>
-  </si>
-  <si>
-    <t>0.0776,0.0037,0.9270,0.0054</t>
-  </si>
-  <si>
-    <t>0.0217,0.0193,0.9250,0.0740</t>
-  </si>
-  <si>
-    <t>0.3682,0.0324,0.5854,0.0737</t>
-  </si>
-  <si>
-    <t>0.0524,0.1074,0.8643,0.0237</t>
-  </si>
-  <si>
-    <t>0.0146,0.1192,0.8868,0.0771</t>
-  </si>
-  <si>
-    <t>0.7079,0.0031,0.0068,0.4334</t>
-  </si>
-  <si>
-    <t>0.0380,0.0088,0.0060,0.9826</t>
-  </si>
-  <si>
-    <t>0.1111,0.0148,0.0009,0.9550</t>
-  </si>
-  <si>
-    <t>0.0145,0.0002,0.0002,0.9961</t>
-  </si>
-  <si>
-    <t>0.0129,0.0006,0.0001,0.9957</t>
-  </si>
-  <si>
-    <t>0.3028,0.0199,0.0316,0.7944</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9139,0.0457,0.0131,0.0181</t>
+  </si>
+  <si>
+    <t>0.1046,0.0027,0.0044,0.9572</t>
+  </si>
+  <si>
+    <t>0.8011,0.0417,0.0042,0.1574</t>
+  </si>
+  <si>
+    <t>0.0271,0.0051,0.0005,0.9917</t>
+  </si>
+  <si>
+    <t>0.9954,0.0023,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0013,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9940,0.0024,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0030,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9846,0.0228,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0031,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8208,0.0285,0.1735,0.0091</t>
+  </si>
+  <si>
+    <t>0.3428,0.0127,0.7568,0.0036</t>
+  </si>
+  <si>
+    <t>0.5662,0.1415,0.3649,0.0092</t>
+  </si>
+  <si>
+    <t>0.1993,0.0350,0.8180,0.0019</t>
+  </si>
+  <si>
+    <t>0.6719,0.0949,0.3420,0.0191</t>
+  </si>
+  <si>
+    <t>0.0113,0.9874,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.0039,0.9909,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.0382,0.9519,0.0057,0.0043</t>
+  </si>
+  <si>
+    <t>0.0111,0.9790,0.0016,0.0044</t>
+  </si>
+  <si>
+    <t>0.0047,0.9897,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.5582,0.0040,0.5061,0.0147</t>
+  </si>
+  <si>
+    <t>0.1912,0.0083,0.8276,0.0096</t>
+  </si>
+  <si>
+    <t>0.0809,0.0218,0.9092,0.0031</t>
+  </si>
+  <si>
+    <t>0.3024,0.0065,0.7828,0.0074</t>
+  </si>
+  <si>
+    <t>0.4419,0.0033,0.6310,0.0111</t>
+  </si>
+  <si>
+    <t>0.0054,0.0017,0.9813,0.0202</t>
+  </si>
+  <si>
+    <t>0.0071,0.0026,0.9813,0.0158</t>
+  </si>
+  <si>
+    <t>0.6483,0.4621,0.0165,0.0013</t>
+  </si>
+  <si>
+    <t>0.5473,0.3722,0.1081,0.0070</t>
+  </si>
+  <si>
+    <t>0.0005,0.0036,0.9967,0.0035</t>
+  </si>
+  <si>
+    <t>0.0092,0.9701,0.0193,0.0005</t>
+  </si>
+  <si>
+    <t>0.9541,0.0342,0.0029,0.0032</t>
+  </si>
+  <si>
+    <t>0.9425,0.0321,0.0182,0.0034</t>
+  </si>
+  <si>
+    <t>0.5693,0.5837,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.0204,0.9589,0.2569,0.0023</t>
+  </si>
+  <si>
+    <t>0.0156,0.8916,0.2430,0.0333</t>
+  </si>
+  <si>
+    <t>0.0396,0.0755,0.9513,0.0053</t>
+  </si>
+  <si>
+    <t>0.0221,0.1054,0.9312,0.0150</t>
+  </si>
+  <si>
+    <t>0.0203,0.0039,0.9581,0.0219</t>
+  </si>
+  <si>
+    <t>0.0062,0.2841,0.9504,0.0016</t>
+  </si>
+  <si>
+    <t>0.0062,0.9627,0.0355,0.0010</t>
+  </si>
+  <si>
+    <t>0.0148,0.0029,0.9666,0.0207</t>
+  </si>
+  <si>
+    <t>0.0101,0.7941,0.0083,0.8629</t>
+  </si>
+  <si>
+    <t>0.0404,0.9526,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.0028,0.9848,0.1075,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9972,0.0842,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.0977,0.9753,0.0064</t>
+  </si>
+  <si>
+    <t>0.0027,0.3347,0.9826,0.0011</t>
+  </si>
+  <si>
+    <t>0.1832,0.0174,0.8492,0.0059</t>
+  </si>
+  <si>
+    <t>0.0636,0.0028,0.9402,0.0069</t>
+  </si>
+  <si>
+    <t>0.0213,0.0134,0.9651,0.0060</t>
+  </si>
+  <si>
+    <t>0.0132,0.2698,0.9243,0.0043</t>
+  </si>
+  <si>
+    <t>0.9090,0.1248,0.0074,0.0024</t>
+  </si>
+  <si>
+    <t>0.9931,0.0022,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9872,0.0040,0.0008,0.0027</t>
+  </si>
+  <si>
+    <t>0.0027,0.0882,0.9877,0.0037</t>
+  </si>
+  <si>
+    <t>0.9744,0.0159,0.0092,0.0008</t>
+  </si>
+  <si>
+    <t>0.9862,0.0054,0.0024,0.0023</t>
+  </si>
+  <si>
+    <t>0.9682,0.0284,0.0041,0.0015</t>
+  </si>
+  <si>
+    <t>0.0035,0.8242,0.9018,0.0039</t>
+  </si>
+  <si>
+    <t>0.0067,0.0098,0.9879,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.0010,0.9904,0.0050</t>
+  </si>
+  <si>
+    <t>0.0005,0.9603,0.9575,0.0003</t>
+  </si>
+  <si>
+    <t>0.0089,0.0018,0.9910,0.0005</t>
+  </si>
+  <si>
+    <t>0.2110,0.8324,0.0076,0.0002</t>
+  </si>
+  <si>
+    <t>0.0152,0.9757,0.0063,0.0003</t>
+  </si>
+  <si>
+    <t>0.4167,0.0976,0.6403,0.0049</t>
+  </si>
+  <si>
+    <t>0.7900,0.2381,0.0255,0.0018</t>
+  </si>
+  <si>
+    <t>0.0014,0.0235,0.9924,0.0022</t>
+  </si>
+  <si>
+    <t>0.0016,0.9188,0.8112,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9455,0.9721,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9923,0.1081,0.0002</t>
+  </si>
+  <si>
+    <t>0.0090,0.9465,0.2527,0.0021</t>
+  </si>
+  <si>
+    <t>0.0159,0.0027,0.0352,0.9749</t>
+  </si>
+  <si>
+    <t>0.0057,0.0038,0.0003,0.9968</t>
+  </si>
+  <si>
+    <t>0.0014,0.1997,0.0010,0.9949</t>
+  </si>
+  <si>
+    <t>0.0229,0.0255,0.0119,0.9760</t>
+  </si>
+  <si>
+    <t>0.0197,0.0087,0.0243,0.9786</t>
+  </si>
+  <si>
+    <t>0.0190,0.0005,0.0017,0.9921</t>
+  </si>
+  <si>
+    <t>0.0003,0.9927,0.5675,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.3506,0.9783,0.0001</t>
+  </si>
+  <si>
+    <t>0.0087,0.6422,0.8821,0.0015</t>
+  </si>
+  <si>
+    <t>0.0058,0.7528,0.8363,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9827,0.9273,0.0000</t>
+  </si>
+  <si>
+    <t>0.0077,0.7997,0.8615,0.0025</t>
+  </si>
+  <si>
+    <t>0.9924,0.0026,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9668,0.0586,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9740,0.0252,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.9917,0.0021,0.0005,0.0019</t>
+  </si>
+  <si>
+    <t>0.9899,0.0051,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9503,0.0519,0.0081,0.0012</t>
+  </si>
+  <si>
+    <t>0.9644,0.0316,0.0088,0.0014</t>
+  </si>
+  <si>
+    <t>0.9722,0.0251,0.0023,0.0020</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9899,0.0066,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0008,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0217,0.0024,0.9731,0.0048</t>
+  </si>
+  <si>
+    <t>0.0510,0.0096,0.9288,0.0130</t>
+  </si>
+  <si>
+    <t>0.7157,0.0300,0.2230,0.0394</t>
+  </si>
+  <si>
+    <t>0.0887,0.0056,0.9404,0.0006</t>
+  </si>
+  <si>
+    <t>0.0187,0.9722,0.0039,0.0016</t>
+  </si>
+  <si>
+    <t>0.0075,0.9833,0.0017,0.0028</t>
+  </si>
+  <si>
+    <t>0.0607,0.9244,0.0043,0.0072</t>
+  </si>
+  <si>
+    <t>0.5958,0.4510,0.0214,0.0064</t>
+  </si>
+  <si>
+    <t>0.0223,0.9629,0.0016,0.0026</t>
+  </si>
+  <si>
+    <t>0.0035,0.9913,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.3419,0.7488,0.0048,0.0028</t>
+  </si>
+  <si>
+    <t>0.7737,0.0459,0.1763,0.0159</t>
+  </si>
+  <si>
+    <t>0.4719,0.0180,0.6499,0.0076</t>
+  </si>
+  <si>
+    <t>0.5265,0.1622,0.3428,0.0148</t>
+  </si>
+  <si>
+    <t>0.5761,0.0225,0.5207,0.0105</t>
+  </si>
+  <si>
+    <t>0.3535,0.0313,0.6349,0.0718</t>
+  </si>
+  <si>
+    <t>0.0094,0.9879,0.0113,0.0002</t>
+  </si>
+  <si>
+    <t>0.0067,0.9807,0.0045,0.0095</t>
+  </si>
+  <si>
+    <t>0.0059,0.9721,0.0097,0.0746</t>
+  </si>
+  <si>
+    <t>0.0004,0.8676,0.9613,0.0003</t>
+  </si>
+  <si>
+    <t>0.0307,0.9724,0.0149,0.0006</t>
+  </si>
+  <si>
+    <t>0.5941,0.3367,0.1012,0.0014</t>
+  </si>
+  <si>
+    <t>0.2022,0.8476,0.0074,0.0019</t>
+  </si>
+  <si>
+    <t>0.9929,0.0038,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9619,0.0300,0.0077,0.0034</t>
+  </si>
+  <si>
+    <t>0.9943,0.0010,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9681,0.0158,0.0090,0.0051</t>
+  </si>
+  <si>
+    <t>0.9927,0.0013,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9419,0.0165,0.0402,0.0030</t>
+  </si>
+  <si>
+    <t>0.9795,0.0100,0.0040,0.0025</t>
+  </si>
+  <si>
+    <t>0.9668,0.0083,0.0149,0.0055</t>
+  </si>
+  <si>
+    <t>0.0019,0.8843,0.9577,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.9206,0.7036,0.0002</t>
+  </si>
+  <si>
+    <t>0.0505,0.3079,0.7932,0.0020</t>
+  </si>
+  <si>
+    <t>0.0115,0.1673,0.9414,0.0012</t>
+  </si>
+  <si>
+    <t>0.9204,0.0190,0.0467,0.0034</t>
+  </si>
+  <si>
+    <t>0.8212,0.0763,0.0548,0.0244</t>
+  </si>
+  <si>
+    <t>0.5998,0.0049,0.6434,0.0013</t>
+  </si>
+  <si>
+    <t>0.8171,0.0261,0.1655,0.0109</t>
+  </si>
+  <si>
+    <t>0.1536,0.0044,0.0038,0.9424</t>
+  </si>
+  <si>
+    <t>0.0016,0.0006,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0009,0.0107,0.0030,0.9976</t>
+  </si>
+  <si>
+    <t>0.0091,0.0010,0.0016,0.9957</t>
+  </si>
+  <si>
+    <t>0.0048,0.9037,0.6824,0.0022</t>
+  </si>
+  <si>
+    <t>0.9351,0.0397,0.0250,0.0043</t>
+  </si>
+  <si>
+    <t>0.0412,0.9479,0.0023,0.0104</t>
+  </si>
+  <si>
+    <t>0.9725,0.0268,0.0018,0.0015</t>
+  </si>
+  <si>
+    <t>0.6345,0.4833,0.0127,0.0051</t>
+  </si>
+  <si>
+    <t>0.9743,0.0113,0.0065,0.0035</t>
+  </si>
+  <si>
+    <t>0.5561,0.0226,0.0319,0.5008</t>
+  </si>
+  <si>
+    <t>0.9865,0.0062,0.0011,0.0019</t>
+  </si>
+  <si>
+    <t>0.0003,0.0497,0.9945,0.0030</t>
+  </si>
+  <si>
+    <t>0.8881,0.0025,0.0055,0.1270</t>
+  </si>
+  <si>
+    <t>0.9692,0.0054,0.0020,0.0127</t>
+  </si>
+  <si>
+    <t>0.4820,0.5221,0.0064,0.0234</t>
+  </si>
+  <si>
+    <t>0.9595,0.0173,0.0075,0.0016</t>
+  </si>
+  <si>
+    <t>0.8489,0.0394,0.1236,0.0081</t>
+  </si>
+  <si>
+    <t>0.0576,0.9309,0.0067,0.0091</t>
+  </si>
+  <si>
+    <t>0.9120,0.0653,0.0172,0.0020</t>
+  </si>
+  <si>
+    <t>0.9296,0.0437,0.0172,0.0042</t>
+  </si>
+  <si>
+    <t>0.9935,0.0013,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9848,0.0107,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9864,0.0070,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9788,0.0046,0.0057,0.0054</t>
+  </si>
+  <si>
+    <t>0.9751,0.0110,0.0024,0.0038</t>
+  </si>
+  <si>
+    <t>0.9846,0.0114,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9776,0.0144,0.0038,0.0021</t>
+  </si>
+  <si>
+    <t>0.9933,0.0013,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.8500,0.2191,0.0102,0.0030</t>
+  </si>
+  <si>
+    <t>0.6961,0.3635,0.0224,0.0041</t>
+  </si>
+  <si>
+    <t>0.7992,0.2233,0.0172,0.0046</t>
+  </si>
+  <si>
+    <t>0.0579,0.5586,0.7906,0.0056</t>
+  </si>
+  <si>
+    <t>0.9104,0.1271,0.0052,0.0019</t>
+  </si>
+  <si>
+    <t>0.8979,0.1064,0.0123,0.0054</t>
+  </si>
+  <si>
+    <t>0.9593,0.0379,0.0036,0.0021</t>
+  </si>
+  <si>
+    <t>0.1174,0.8923,0.0093,0.0036</t>
+  </si>
+  <si>
+    <t>0.0012,0.0476,0.9960,0.0003</t>
+  </si>
+  <si>
+    <t>0.9524,0.0441,0.0029,0.0032</t>
+  </si>
+  <si>
+    <t>0.0060,0.0076,0.9830,0.0026</t>
+  </si>
+  <si>
+    <t>0.0101,0.0316,0.9792,0.0024</t>
+  </si>
+  <si>
+    <t>0.0783,0.0029,0.9477,0.0019</t>
+  </si>
+  <si>
+    <t>0.0056,0.0883,0.9832,0.0003</t>
+  </si>
+  <si>
+    <t>0.0603,0.0120,0.9434,0.0022</t>
+  </si>
+  <si>
+    <t>0.0285,0.0186,0.9684,0.0002</t>
+  </si>
+  <si>
+    <t>0.0060,0.0126,0.9908,0.0003</t>
+  </si>
+  <si>
+    <t>0.0348,0.0073,0.9686,0.0021</t>
+  </si>
+  <si>
+    <t>0.4141,0.0357,0.6248,0.0187</t>
+  </si>
+  <si>
+    <t>0.3658,0.0282,0.6625,0.0115</t>
+  </si>
+  <si>
+    <t>0.7583,0.0921,0.1581,0.0053</t>
+  </si>
+  <si>
+    <t>0.0938,0.1250,0.8396,0.0021</t>
+  </si>
+  <si>
+    <t>0.3496,0.1231,0.5140,0.0058</t>
+  </si>
+  <si>
+    <t>0.6594,0.0918,0.2520,0.0732</t>
+  </si>
+  <si>
+    <t>0.3017,0.1081,0.6425,0.0042</t>
+  </si>
+  <si>
+    <t>0.4760,0.7064,0.0037,0.0007</t>
+  </si>
+  <si>
+    <t>0.1946,0.8757,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.7348,0.3336,0.0215,0.0011</t>
+  </si>
+  <si>
+    <t>0.6980,0.3587,0.0180,0.0008</t>
+  </si>
+  <si>
+    <t>0.7428,0.4287,0.0038,0.0013</t>
+  </si>
+  <si>
+    <t>0.8540,0.0377,0.0667,0.0142</t>
+  </si>
+  <si>
+    <t>0.7900,0.0127,0.2883,0.0034</t>
+  </si>
+  <si>
+    <t>0.6272,0.0196,0.3543,0.0347</t>
+  </si>
+  <si>
+    <t>0.2237,0.0073,0.7787,0.0211</t>
+  </si>
+  <si>
+    <t>0.8129,0.0102,0.2851,0.0023</t>
+  </si>
+  <si>
+    <t>0.0095,0.0041,0.9723,0.0381</t>
+  </si>
+  <si>
+    <t>0.0783,0.1701,0.7938,0.0204</t>
+  </si>
+  <si>
+    <t>0.0084,0.0419,0.9658,0.0035</t>
+  </si>
+  <si>
+    <t>0.1620,0.0086,0.8930,0.0030</t>
+  </si>
+  <si>
+    <t>0.1037,0.2454,0.7751,0.0253</t>
+  </si>
+  <si>
+    <t>0.9902,0.0024,0.0003,0.0023</t>
+  </si>
+  <si>
+    <t>0.9827,0.0195,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9754,0.0221,0.0029,0.0019</t>
+  </si>
+  <si>
+    <t>0.9729,0.0264,0.0025,0.0013</t>
+  </si>
+  <si>
+    <t>0.9587,0.0265,0.0087,0.0039</t>
+  </si>
+  <si>
+    <t>0.9851,0.0119,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9893,0.0037,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9862,0.0084,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.0125,0.0026,0.9741,0.0231</t>
+  </si>
+  <si>
+    <t>0.2431,0.1151,0.7018,0.0155</t>
+  </si>
+  <si>
+    <t>0.8748,0.0380,0.0737,0.0277</t>
+  </si>
+  <si>
+    <t>0.0092,0.0014,0.9908,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0074,0.9942,0.0015</t>
+  </si>
+  <si>
+    <t>0.0187,0.0673,0.9394,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.0020,0.9940,0.0048</t>
+  </si>
+  <si>
+    <t>0.0457,0.0184,0.9408,0.0035</t>
+  </si>
+  <si>
+    <t>0.0009,0.1362,0.9906,0.0009</t>
+  </si>
+  <si>
+    <t>0.0265,0.0235,0.9518,0.0018</t>
+  </si>
+  <si>
+    <t>0.1799,0.2799,0.6689,0.0102</t>
+  </si>
+  <si>
+    <t>0.5692,0.0062,0.3979,0.0283</t>
+  </si>
+  <si>
+    <t>0.8844,0.0088,0.1179,0.0029</t>
+  </si>
+  <si>
+    <t>0.8929,0.0270,0.0679,0.0074</t>
+  </si>
+  <si>
+    <t>0.9704,0.0299,0.0032,0.0014</t>
+  </si>
+  <si>
+    <t>0.9672,0.0438,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.9853,0.0121,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9792,0.0170,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9953,0.0003,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9847,0.0102,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.9941,0.0020,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9731,0.0181,0.0046,0.0022</t>
+  </si>
+  <si>
+    <t>0.0552,0.1103,0.8476,0.0057</t>
+  </si>
+  <si>
+    <t>0.0063,0.0672,0.9723,0.0074</t>
+  </si>
+  <si>
+    <t>0.0075,0.0977,0.9616,0.0056</t>
+  </si>
+  <si>
+    <t>0.0110,0.0086,0.9860,0.0007</t>
+  </si>
+  <si>
+    <t>0.0072,0.0025,0.9853,0.0053</t>
+  </si>
+  <si>
+    <t>0.2498,0.0123,0.7589,0.0460</t>
+  </si>
+  <si>
+    <t>0.0743,0.0225,0.8922,0.0290</t>
+  </si>
+  <si>
+    <t>0.0169,0.0122,0.9625,0.0190</t>
+  </si>
+  <si>
+    <t>0.8918,0.0032,0.0187,0.0655</t>
+  </si>
+  <si>
+    <t>0.0377,0.0255,0.0005,0.9769</t>
+  </si>
+  <si>
+    <t>0.1004,0.0073,0.0018,0.9669</t>
+  </si>
+  <si>
+    <t>0.0099,0.0008,0.0009,0.9947</t>
+  </si>
+  <si>
+    <t>0.0052,0.0000,0.0002,0.9973</t>
+  </si>
+  <si>
+    <t>0.7297,0.0054,0.0017,0.4205</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>261</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
